--- a/data/trans_dic/P42C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Habitat-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -516,39 +516,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -579,21 +569,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -608,9 +583,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -625,17 +597,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,21 +621,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12,94%</t>
         </is>
@@ -678,47 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,73; 21,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,39; 12,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,19; 16,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 20,55</t>
+          <t>13,73; 21,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,73</t>
+          <t>7,39; 12,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 15,99</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,75; 20,55</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,26; 12,73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10,36; 15,99</t>
+          <t>10,19; 16,12</t>
         </is>
       </c>
     </row>
@@ -735,17 +677,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,21 +701,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21,13%</t>
         </is>
@@ -788,47 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,23; 30,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,66; 16,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,17; 24,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,4; 30,98</t>
+          <t>24,23; 30,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 16,44</t>
+          <t>11,66; 16,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,29; 24,05</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,4; 30,98</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11,51; 16,44</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18,29; 24,05</t>
+          <t>18,17; 24,24</t>
         </is>
       </c>
     </row>
@@ -845,17 +757,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,21 +781,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>31,0%</t>
         </is>
@@ -898,47 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,79; 29,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,19; 19,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,04; 35,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,87; 29,13</t>
+          <t>21,79; 29,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,17; 19,36</t>
+          <t>13,19; 19,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,89; 35,97</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>21,87; 29,13</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>13,17; 19,36</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>23,89; 35,97</t>
+          <t>24,04; 35,83</t>
         </is>
       </c>
     </row>
@@ -955,17 +837,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,21 +861,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25,42%</t>
         </is>
@@ -1008,47 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,55; 26,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,08; 22,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,83; 29,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,66; 26,75</t>
+          <t>20,55; 26,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 22,83</t>
+          <t>17,08; 22,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 29,98</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,66; 26,75</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17,07; 22,83</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17,87; 29,98</t>
+          <t>17,83; 29,56</t>
         </is>
       </c>
     </row>
@@ -1065,17 +917,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,21 +941,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>23,2%</t>
         </is>
@@ -1118,47 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,97; 25,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,06; 16,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,01; 25,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,3; 25,73</t>
+          <t>21,97; 25,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 17,01</t>
+          <t>14,06; 16,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,44; 25,25</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,3; 25,73</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14,25; 17,01</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20,44; 25,25</t>
+          <t>20,01; 25,0</t>
         </is>
       </c>
     </row>
@@ -1170,13 +992,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
@@ -1191,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1202,39 +1023,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1265,21 +1076,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1294,9 +1090,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1311,17 +1104,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1335,21 +1128,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
@@ -1364,17 +1142,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1388,21 +1166,6 @@
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46941</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89220</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48545</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46941</t>
         </is>
@@ -1417,47 +1180,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71478; 109615</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36514; 64060</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36964; 58447</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71590; 107013</t>
+          <t>71478; 109615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35866; 62905</t>
+          <t>36514; 64060</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37572; 57971</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>71590; 107013</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35866; 62905</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>37572; 57971</t>
+          <t>36964; 58447</t>
         </is>
       </c>
     </row>
@@ -1474,17 +1222,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1498,21 +1246,6 @@
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>178</t>
         </is>
@@ -1527,17 +1260,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214834</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1551,21 +1284,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>116043</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>214834</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>117083</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>116043</t>
         </is>
@@ -1580,47 +1298,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>188148; 240411</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>98329; 138460</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>99789; 133104</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>189518; 240607</t>
+          <t>188148; 240411</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>97100; 138643</t>
+          <t>98329; 138460</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>100442; 132070</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>189518; 240607</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>97100; 138643</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>100442; 132070</t>
+          <t>99789; 133104</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1340,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1661,21 +1364,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>187</t>
         </is>
@@ -1690,17 +1378,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160802</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97428</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1714,21 +1402,6 @@
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>133077</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>160802</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97428</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>133077</t>
         </is>
@@ -1743,47 +1416,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>138846; 186231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>79496; 115551</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>103204; 153801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>139352; 185597</t>
+          <t>138846; 186231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79406; 116676</t>
+          <t>79496; 115551</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>102577; 154413</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>139352; 185597</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>79406; 116676</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>102577; 154413</t>
+          <t>103204; 153801</t>
         </is>
       </c>
     </row>
@@ -1800,17 +1458,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1824,21 +1482,6 @@
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>262</t>
         </is>
@@ -1853,17 +1496,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190820</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166475</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1877,21 +1520,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>171276</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>190820</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>166475</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171276</t>
         </is>
@@ -1906,47 +1534,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>165527; 215819</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>142855; 189551</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>120157; 199195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166384; 215484</t>
+          <t>165527; 215819</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142770; 190902</t>
+          <t>142855; 189551</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>120434; 202002</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>166384; 215484</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>142770; 190902</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>120434; 202002</t>
+          <t>120157; 199195</t>
         </is>
       </c>
     </row>
@@ -1963,17 +1576,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>404</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1987,21 +1600,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>711</t>
         </is>
@@ -2016,17 +1614,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655675</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429531</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2040,21 +1638,6 @@
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>467337</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>655675</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>429531</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>467337</t>
         </is>
@@ -2069,47 +1652,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>601929; 701351</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>390425; 470981</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>403168; 503641</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>611083; 705108</t>
+          <t>601929; 701351</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>395628; 472258</t>
+          <t>390425; 470981</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>411727; 508802</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>611083; 705108</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>395628; 472258</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>411727; 508802</t>
+          <t>403168; 503641</t>
         </is>
       </c>
     </row>
@@ -2121,14 +1689,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P42C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Habitat-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,73; 21,05</t>
+          <t>13,98; 21,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,97</t>
+          <t>7,45; 12,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,19; 16,12</t>
+          <t>10,48; 15,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,73; 21,05</t>
+          <t>13,98; 21,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,97</t>
+          <t>7,45; 12,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,19; 16,12</t>
+          <t>10,48; 15,93</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,23; 30,96</t>
+          <t>24,6; 31,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,41</t>
+          <t>11,52; 16,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,17; 24,24</t>
+          <t>18,53; 24,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,23; 30,96</t>
+          <t>24,6; 31,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,41</t>
+          <t>11,52; 16,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,17; 24,24</t>
+          <t>18,53; 24,57</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,79; 29,23</t>
+          <t>22,06; 28,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,17</t>
+          <t>13,21; 19,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,04; 35,83</t>
+          <t>28,04; 36,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,79; 29,23</t>
+          <t>22,06; 28,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,17</t>
+          <t>13,21; 19,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,04; 35,83</t>
+          <t>28,04; 36,22</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,55; 26,79</t>
+          <t>20,89; 26,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 22,67</t>
+          <t>17,13; 22,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,83; 29,56</t>
+          <t>25,34; 31,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,55; 26,79</t>
+          <t>20,89; 26,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 22,67</t>
+          <t>17,13; 22,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,83; 29,56</t>
+          <t>25,34; 31,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,97; 25,6</t>
+          <t>22,29; 25,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,96</t>
+          <t>14,19; 16,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,01; 25,0</t>
+          <t>22,61; 26,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,97; 25,6</t>
+          <t>22,29; 25,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,96</t>
+          <t>14,19; 16,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,01; 25,0</t>
+          <t>22,61; 26,0</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46941</t>
+          <t>49984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46941</t>
+          <t>49984</t>
         </is>
       </c>
     </row>
@@ -1180,32 +1180,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71478; 109615</t>
+          <t>72808; 109582</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36514; 64060</t>
+          <t>36812; 63066</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36964; 58447</t>
+          <t>40710; 61893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71478; 109615</t>
+          <t>72808; 109582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36514; 64060</t>
+          <t>36812; 63066</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36964; 58447</t>
+          <t>40710; 61893</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116043</t>
+          <t>130922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>116043</t>
+          <t>130922</t>
         </is>
       </c>
     </row>
@@ -1298,32 +1298,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>188148; 240411</t>
+          <t>191064; 244607</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>98329; 138460</t>
+          <t>97192; 137046</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99789; 133104</t>
+          <t>112878; 149671</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>188148; 240411</t>
+          <t>191064; 244607</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>98329; 138460</t>
+          <t>97192; 137046</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99789; 133104</t>
+          <t>112878; 149671</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133077</t>
+          <t>147354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>133077</t>
+          <t>147354</t>
         </is>
       </c>
     </row>
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>138846; 186231</t>
+          <t>140548; 184094</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79496; 115551</t>
+          <t>79651; 116388</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103204; 153801</t>
+          <t>129332; 167052</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138846; 186231</t>
+          <t>140548; 184094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79496; 115551</t>
+          <t>79651; 116388</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>103204; 153801</t>
+          <t>129332; 167052</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171276</t>
+          <t>184565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>171276</t>
+          <t>184565</t>
         </is>
       </c>
     </row>
@@ -1534,32 +1534,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>165527; 215819</t>
+          <t>168252; 217254</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>142855; 189551</t>
+          <t>143258; 191480</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120157; 199195</t>
+          <t>165001; 206037</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>165527; 215819</t>
+          <t>168252; 217254</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142855; 189551</t>
+          <t>143258; 191480</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>120157; 199195</t>
+          <t>165001; 206037</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
     </row>
@@ -1652,32 +1652,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>601929; 701351</t>
+          <t>610767; 709432</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>390425; 470981</t>
+          <t>393932; 471432</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>403168; 503641</t>
+          <t>477218; 548651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>601929; 701351</t>
+          <t>610767; 709432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>390425; 470981</t>
+          <t>393932; 471432</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>403168; 503641</t>
+          <t>477218; 548651</t>
         </is>
       </c>
     </row>
